--- a/Fatture/Registro-Spese.xlsx
+++ b/Fatture/Registro-Spese.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-09 13:45:19</t>
+          <t>2026-09-01 09:22:47</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>23.3</v>
+        <v>49.24</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>4.2</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>234.24</v>
+        <v>250.1</v>
       </c>
     </row>
     <row r="14">
@@ -570,7 +570,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-13 — IONOS VPS Linux L+ (trainmind-vps) (65 gg)</t>
+          <t>2026-10-13 — IONOS VPS Linux L+ (trainmind-vps) (42 gg)</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -891,6 +891,75 @@
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Infrastruttura</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IONOS VPS Linux L+</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>109994167317</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ionos/Fattura_2026-08-16_109994167317_V112969652.pdf</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -902,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -947,6 +1016,22 @@
       </c>
       <c r="D2" s="4" t="n">
         <v>23.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>25.94</v>
       </c>
     </row>
   </sheetData>
@@ -1239,7 +1324,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1272,7 +1357,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1331,7 +1416,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
@@ -1341,7 +1426,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
@@ -1351,17 +1436,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>6.1</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
@@ -1371,7 +1456,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -1381,7 +1466,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
@@ -1391,7 +1476,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
@@ -1401,7 +1486,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2027-04</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -1411,7 +1496,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2027-04</t>
+          <t>2027-05</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
@@ -1421,7 +1506,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2027-05</t>
+          <t>2027-06</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
@@ -1431,21 +1516,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2027-06</t>
+          <t>2027-07</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>21.96</v>
+        <v>40.26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2027-07</t>
+          <t>2027-08</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>40.26</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="14">
@@ -1455,7 +1540,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>234.24</v>
+        <v>250.1</v>
       </c>
     </row>
   </sheetData>
@@ -1495,7 +1580,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>4.2</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -1505,7 +1590,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>4.2</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1593,7 +1678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1890,6 +1975,161 @@
         <v>22</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>109994167317</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Tariﬀa base</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G10" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>109994167317</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sconto</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-13</v>
+      </c>
+      <c r="G11" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>109994167317</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>IP addizionale</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>109994167317</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>IONOS Cloud</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="G13" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>109994167317</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IP addizionale</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Fatture/Registro-Spese.xlsx
+++ b/Fatture/Registro-Spese.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 09:22:47</t>
+          <t>2026-09-08 09:30:52</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>49.24</v>
+        <v>57.17</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>8.880000000000001</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="8">
@@ -570,7 +570,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-13 — IONOS VPS Linux L+ (trainmind-vps) (42 gg)</t>
+          <t>2026-10-13 — IONOS VPS Linux L+ (trainmind-vps) (35 gg)</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -960,6 +960,144 @@
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Infrastruttura</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>IONOS Pack Dominio</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>109994206417</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2027-09-06</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>ionos/IONOS fattura 2026-09-08 - FA_109994206417.pdf</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Infrastruttura</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>IONOS Pack Dominio</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>109994206419</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>ionos/IONOS fattura 2026-09-08 - FA_109994206419.pdf</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -971,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1032,6 +1170,22 @@
       </c>
       <c r="D3" s="4" t="n">
         <v>25.94</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>7.93</v>
       </c>
     </row>
   </sheetData>
@@ -1324,7 +1478,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1357,7 +1511,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1580,7 +1734,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>8.880000000000001</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="3">
@@ -1590,7 +1744,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>8.880000000000001</v>
+        <v>10.31</v>
       </c>
     </row>
   </sheetData>
@@ -1678,7 +1832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2130,6 +2284,99 @@
         <v>22</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>109994206417</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Dominio .com</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G15" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>109994206417</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sconto</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G16" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>109994206419</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>IONOS Mail Basic 1</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Fatture/Registro-Spese.xlsx
+++ b/Fatture/Registro-Spese.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-08 09:30:52</t>
+          <t>2026-10-06 11:47:08</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>57.17</v>
+        <v>81.72</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>10.31</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>250.1</v>
+        <v>265.96</v>
       </c>
     </row>
     <row r="14">
@@ -570,7 +570,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-13 — IONOS VPS Linux L+ (trainmind-vps) (35 gg)</t>
+          <t>2026-10-13 — IONOS VPS Linux L+ (trainmind-vps) (7 gg)</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1098,6 +1098,75 @@
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Infrastruttura</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>IONOS VPS Linux L+</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>109994221094</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>ionos/Fattura_2026-09-16_109994221094_V112969652.pdf</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1179,13 +1248,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>6.5</v>
+        <v>26.62</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1.43</v>
+        <v>5.86</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>7.93</v>
+        <v>32.48</v>
       </c>
     </row>
   </sheetData>
@@ -1478,11 +1547,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1511,7 +1580,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1570,7 +1639,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="B2" s="4" t="n">
@@ -1580,17 +1649,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>6.1</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
@@ -1600,7 +1669,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
@@ -1610,7 +1679,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
@@ -1620,7 +1689,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
@@ -1630,7 +1699,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2027-04</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
@@ -1640,7 +1709,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2027-04</t>
+          <t>2027-05</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
@@ -1650,7 +1719,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2027-05</t>
+          <t>2027-06</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
@@ -1660,27 +1729,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2027-06</t>
+          <t>2027-07</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>21.96</v>
+        <v>40.26</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2027-07</t>
+          <t>2027-08</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>40.26</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2027-08</t>
+          <t>2027-09</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
@@ -1694,7 +1763,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>250.1</v>
+        <v>265.96</v>
       </c>
     </row>
   </sheetData>
@@ -1734,7 +1803,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>10.31</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="3">
@@ -1744,7 +1813,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>10.31</v>
+        <v>14.74</v>
       </c>
     </row>
   </sheetData>
@@ -1832,7 +1901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2377,6 +2446,192 @@
         <v>22</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>109994221094</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Tariﬀa base</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G18" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>109994221094</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sconto</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>-13</v>
+      </c>
+      <c r="G19" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>109994221094</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>IP addizionale</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>109994221094</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>IONOS Cloud</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="G21" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>109994221094</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IONOS Cloud</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G22" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>IONOS SE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>109994221094</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>IP addizionale</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
